--- a/hbn_df.xlsx
+++ b/hbn_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G176"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,54 +468,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>149</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>아주대학교의료원</t>
+          <t>DGIST</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026학년도 2학기 특별임용교원(진료교수) 초빙</t>
+          <t>2026년도 대학원 제2차/기술경영전문대학원 일반 전임직교원 공개초빙</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.09</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26.06.29</t>
+          <t>26.06.30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.09</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3584332?pagekey=3584332&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584238</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>148</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>주안대학원대학교</t>
+          <t>아주대학교의료원</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>전임교원 초빙</t>
+          <t>2026학년도 2학기 특별임용교원(진료교수) 초빙</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -535,34 +535,34 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3584407?pagekey=3584407&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584332</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>147</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>남부대학교</t>
+          <t>주안대학원대학교</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026학년도 하반기 전임교원 초빙</t>
+          <t>전임교원 초빙</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>26.06.15</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26.06.22</t>
+          <t>26.06.29</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,24 +572,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3584355?pagekey=3584355&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584407</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>146</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>한신대학교</t>
+          <t>남부대학교</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026학년도 2학기 전임교원 초빙</t>
+          <t>2026학년도 하반기 전임교원 초빙</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -609,34 +609,34 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3584386?pagekey=3584386&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584355</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>145</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>나사렛대학교</t>
+          <t>한신대학교</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026학년도 2학기 교수 초빙</t>
+          <t>2026학년도 2학기 전임교원 초빙</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>26.06.23</t>
+          <t>26.06.22</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -646,34 +646,34 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3584325?pagekey=3584325&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584386</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>144</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>고려대학교</t>
+          <t>나사렛대학교</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>미래성장연구원 연구교수/박사후연구원 임용</t>
+          <t>2026학년도 2학기 교수 초빙</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>26.06.15</t>
+          <t>26.06.23</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -683,34 +683,34 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3584196?pagekey=3584196&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584325</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>143</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>대전보건대학교</t>
+          <t>고려대학교</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026학년도 2학기 교수 초빙</t>
+          <t>미래성장연구원 연구교수/박사후연구원 임용</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>26.06.22</t>
+          <t>26.06.15</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -720,24 +720,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3584151?pagekey=3584151&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584196</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>경북보건대학교</t>
+          <t>연세대학교</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026학년도 2학기 전임교원 초빙</t>
+          <t>국어국문학과 학술연구교수 모집</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>26.06.22</t>
+          <t>26.06.23</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3584198?pagekey=3584198&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584335</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>연세대학교</t>
+          <t>고려대학교</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>국어국문학과 학술연구교수 모집</t>
+          <t>대학정책연구원 연구교수 모집</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>26.06.23</t>
+          <t>26.06.16</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -794,34 +794,34 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3584335?pagekey=3584335&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584249</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>고려대학교</t>
+          <t>서울외국어대학원대학교</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>대학정책연구원 연구교수 모집</t>
+          <t>겸임/특임교원 모집</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>26.06.16</t>
+          <t>26.06.26</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -831,34 +831,34 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3584249?pagekey=3584249&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583976</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>서울외국어대학원대학교</t>
+          <t>한국폴리텍특성화대학</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>겸임/특임교원 모집</t>
+          <t>반도체융합캠퍼스 산학협력중점교수 모집</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>26.06.15</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>26.06.26</t>
+          <t>26.06.18</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -868,24 +868,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3583976?pagekey=3583976&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584273</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>한국폴리텍특성화대학</t>
+          <t>이화여자대학교</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>반도체융합캠퍼스 산학협력중점교수 모집</t>
+          <t>경영전문대학원 특임교수 모집</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>26.06.18</t>
+          <t>26.06.13</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -905,24 +905,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3584273?pagekey=3584273&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584334</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>이화여자대학교</t>
+          <t>서울대학교</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>경영전문대학원 특임교수 모집</t>
+          <t>천연물과학연구소 연구교원 모집 (8차)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>26.06.13</t>
+          <t>26.06.15</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -942,24 +942,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3584334?pagekey=3584334&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584290</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>서울대학교</t>
+          <t>서울대학교병원</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>천연물과학연구소 연구교원 모집 (8차)</t>
+          <t>진료교수요원/진료의 모집</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -979,24 +979,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3584290?pagekey=3584290&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584265</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>서울대학교병원</t>
+          <t>전주대학교</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>진료교수요원/진료의 모집</t>
+          <t>비전임교원 모집</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>26.06.15</t>
+          <t>26.06.12</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1016,34 +1016,34 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3584265?pagekey=3584265&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584307</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>134</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>전주대학교</t>
+          <t>울산대학교</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>비전임교원 모집</t>
+          <t>경영경제융합학부 연구교원 모집</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.06</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>26.06.12</t>
+          <t>내일마감</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1053,71 +1053,71 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3584307?pagekey=3584307&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584213</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>133</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>울산대학교</t>
+          <t>경북대학교</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>경영경제융합학부 연구교원 모집</t>
+          <t>장수생활과학연구소 연구초빙교수 모집</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>26.06.06</t>
+          <t>26.06.10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.11</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3584213?pagekey=3584213&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584271</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>경북대학교</t>
+          <t>서울대학교병원</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>장수생활과학연구소 연구초빙교수 모집</t>
+          <t>의생명연구원 연구교수 모집</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>26.06.10</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>26.06.11</t>
+          <t>26.06.15</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1127,24 +1127,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3584271?pagekey=3584271&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584264</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>서울대학교병원</t>
+          <t>한국폴리텍IV대학</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>의생명연구원 연구교수 모집</t>
+          <t>충주캠퍼스 산학협력중점교수 모집</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>26.06.15</t>
+          <t>26.06.21</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1164,36 +1164,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3584264?pagekey=3584264&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584064</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>130</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>한국폴리텍IV대학</t>
+          <t>단국대학교</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>충주캠퍼스 산학협력중점교수 모집</t>
+          <t>의료원 내과중환자실 임상전담교원 및 촉탁의 모집</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>26.06.08</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>26.06.21</t>
-        </is>
-      </c>
+          <t>채용시까지</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>26.06.08</t>
@@ -1201,28 +1197,36 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3584064?pagekey=3584064&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584100</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>단국대학교</t>
+          <t>경북대학교병원</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>의료원 내과중환자실 임상전담교원 및 촉탁의 모집</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+          <t>산부인과 진료교수 모집 (22차)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>26.06.05</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>26.06.12</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>26.06.08</t>
@@ -1230,34 +1234,34 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3584100?pagekey=3584100&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584212</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>경북대학교병원</t>
+          <t>대전보건대학교</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>산부인과 진료교수 모집 (22차)</t>
+          <t>2026학년도 2학기 교수 초빙</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>26.06.12</t>
+          <t>26.06.22</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1267,167 +1271,167 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3584212?pagekey=3584212&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584151</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>서정대학교</t>
+          <t>경북보건대학교</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026학년도 2학기 전임교원 초빙 (1차)</t>
+          <t>2026학년도 2학기 전임교원 초빙</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>26.06.01</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>26.06.15</t>
+          <t>26.06.22</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>26.06.02</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3583508?pagekey=3583508&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584198</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>한성대학교</t>
+          <t>서정대학교</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026학년도 2학기 전임교원 초빙</t>
+          <t>2026학년도 2학기 전임교원 초빙 (1차)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>26.06.01</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>26.06.15</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>26.06.02</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>26.05.28</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>20790</t>
-        </is>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3582988?pagekey=3582988&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583508</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KAIST</t>
+          <t>한성대학교</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>수리과학과 전임직 교원 모집</t>
+          <t>2026학년도 2학기 전임교원 초빙</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>26.06.15</t>
+          <t>26.06.02</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>26.07.31</t>
+          <t>내일마감</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.05.28</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/categories/JOB/categories/PROF/recruits/3583905?pagekey=3583905&amp;listType=ING&amp;pagesize=10&amp;sortType=SORTDTM&amp;cntType=JOB&amp;limit=25&amp;displayType=TIT&amp;siteid=1&amp;page=1</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3582988</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>아주대학교의료원</t>
+          <t>KAIST</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026학년도 2학기 특별임용교원(진료교수) 초빙</t>
+          <t>수리과학과 전임직 교원 모집</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.15</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>26.06.29</t>
+          <t>26.07.31</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584332</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583905</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>주안대학원대학교</t>
+          <t>연암대학교</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1437,817 +1441,809 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>26.06.29</t>
+          <t>26.06.18</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584407</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583885</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>남부대학교</t>
+          <t>서울디지털대학교</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026학년도 하반기 전임교원 초빙</t>
+          <t>비전임교원 모집</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>26.06.15</t>
+          <t>26.06.10</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>26.06.22</t>
+          <t>26.06.17</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584355</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584033</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>한신대학교</t>
+          <t>경남대학교</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026학년도 2학기 전임교원 초빙</t>
+          <t>2026학년도 제2학기 전임교원 초빙</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>26.06.15</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>26.06.22</t>
+          <t>26.06.19</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584386</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584041</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>나사렛대학교</t>
+          <t>국립순천대학교</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026학년도 2학기 교수 초빙</t>
+          <t>글로컬대학사업 비전임교원 및 연구원 모집</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>26.06.23</t>
+          <t>26.06.12</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584325</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584101</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>고려대학교</t>
+          <t>동명대학교</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>미래성장연구원 연구교수/박사후연구원 임용</t>
+          <t>교육혁신센터 초빙교수 모집</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>26.06.15</t>
+          <t>26.06.12</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584196</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583975</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>대전보건대학교</t>
+          <t>두원공과대학교</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026학년도 2학기 교수 초빙</t>
+          <t>AX교양학부 초빙교원 모집</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>26.06.22</t>
+          <t>26.06.11</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584151</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584097</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>경북보건대학교</t>
+          <t>경북대학교</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026학년도 2학기 전임교원 초빙</t>
+          <t>2026학년도 제2차 교수 초빙</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.07.21</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>26.06.22</t>
+          <t>26.07.31</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.05.27</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584198</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3571083</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>연세대학교</t>
+          <t>한림대학교</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>국어국문학과 학술연구교수 모집</t>
+          <t>스타트업비즈니스전공 겸임교원 모집</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>26.06.23</t>
+          <t>내일마감</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584335</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583981</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>고려대학교</t>
+          <t>GIST</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>대학정책연구원 연구교수 모집</t>
+          <t>언어교육원 비전임직교원(대우교수) 채용</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>26.06.16</t>
+          <t>26.06.21</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584249</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584061</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>서울외국어대학원대학교</t>
+          <t>한라대학교</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>겸임/특임교원 모집</t>
+          <t>특별교원 모집 (7차)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>26.06.15</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>26.06.26</t>
+          <t>내일마감</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583976</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583979</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>한국폴리텍특성화대학</t>
+          <t>한경국립대학교</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>반도체융합캠퍼스 산학협력중점교수 모집</t>
+          <t>공군학군단 초빙교원 모집</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>26.06.18</t>
+          <t>26.06.11</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584273</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583980</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>이화여자대학교</t>
+          <t>혜전대학교</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>경영전문대학원 특임교수 모집</t>
+          <t>교수 초빙</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.05.29</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>26.06.13</t>
+          <t>26.06.12</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584334</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583123</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>서울대학교</t>
+          <t>DGIST</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>천연물과학연구소 연구교원 모집 (8차)</t>
+          <t>초빙강의교수 모집</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>26.06.15</t>
+          <t>26.06.19</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584290</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583964</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>서울대학교병원</t>
+          <t>세한대학교</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>진료교수요원/진료의 모집</t>
+          <t>특수신분교원 모집</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>26.06.15</t>
+          <t>내일마감</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584265</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583978</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>109</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>전주대학교</t>
+          <t>경상국립대학교</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>비전임교원 모집</t>
+          <t>농업생명과학연구원 초빙교원 모집</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>26.06.12</t>
+          <t>내일마감</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584307</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583974</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>울산대학교</t>
+          <t>대구과학대학교</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>경영경제융합학부 연구교원 모집</t>
+          <t>간호학과 2026학년도 2학기 전임교원 초빙</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>26.06.06</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>내일마감</t>
+          <t>26.06.19</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584213</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584020</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>107</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>경북대학교</t>
+          <t>신성대학교</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>장수생활과학연구소 연구초빙교수 모집</t>
+          <t>전임교원 초빙</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>26.06.10</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>26.06.11</t>
+          <t>26.06.19</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584271</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583968</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>서울대학교병원</t>
+          <t>한라대학교</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>의생명연구원 연구교수 모집</t>
+          <t>전임 및 비전임 교원 초빙</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>26.06.08</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>26.06.15</t>
-        </is>
-      </c>
+          <t>공고문참조</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584264</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583827</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>한국폴리텍IV대학</t>
+          <t>전남대학교</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>충주캠퍼스 산학협력중점교수 모집</t>
+          <t>인공지능혁신융합대학사업단 비전임교원 모집</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.02</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>26.06.21</t>
+          <t>26.06.17</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584064</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583808</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>104</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>단국대학교</t>
+          <t>가톨릭대학교</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>의료원 내과중환자실 임상전담교원 및 촉탁의 모집</t>
+          <t>성의교정 가톨릭대학교 인문사회의학과 교원 초빙</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>채용시까지</t>
+          <t>공고문참조</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584100</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583805</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>경북대학교병원</t>
+          <t>서울대학교</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>산부인과 진료교수 모집 (22차)</t>
+          <t>공과대학 협동과정 기술경영경제정책 전공 외국인 교원 인재풀 모집</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>26.06.12</t>
-        </is>
-      </c>
+          <t>공고문참조</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584212</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583951</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>서정대학교</t>
+          <t>서울대학교</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026학년도 2학기 전임교원 초빙 (1차)</t>
+          <t>국제농업기술대학원 특임교원 모집</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>26.06.01</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>26.06.15</t>
+          <t>내일마감</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>26.06.02</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583508</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583918</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>101</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>한성대학교</t>
+          <t>이화여자대학교</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026학년도 2학기 전임교원 초빙</t>
+          <t>이화인문과학원 인문사회학술연구교수 모집</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>26.06.02</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2257,71 +2253,67 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>26.05.28</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3582988</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583908</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>KAIST</t>
+          <t>한양대학교</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>수리과학과 전임직 교원 모집</t>
+          <t>ERICA캠퍼스 겸임교수/강사 모집</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>26.06.15</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>26.07.31</t>
-        </is>
-      </c>
+          <t>관련URL참조</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583905</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583718</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>연암대학교</t>
+          <t>한국교원대학교</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>전임교원 초빙</t>
+          <t>초빙교원 모집</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2331,367 +2323,367 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583885</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584240</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>서울디지털대학교</t>
+          <t>서울외국어대학원대학교</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>비전임교원 모집</t>
+          <t>겸임/특임교원 모집</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>26.06.10</t>
+          <t>26.06.15</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>26.06.17</t>
+          <t>26.06.26</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584033</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583976</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>경남대학교</t>
+          <t>한국폴리텍특성화대학</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026학년도 제2학기 전임교원 초빙</t>
+          <t>반도체융합캠퍼스 산학협력중점교수 모집</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>26.06.19</t>
+          <t>26.06.18</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584041</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584273</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>국립순천대학교</t>
+          <t>연세대학교</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>글로컬대학사업 비전임교원 및 연구원 모집</t>
+          <t>간호대학 LT강사 모집</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>26.06.12</t>
+          <t>26.06.19</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584101</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584283</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>동명대학교</t>
+          <t>서울대학교</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>교육혁신센터 초빙교수 모집</t>
+          <t>사범대학 강사 모집 (2차 추가)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.11</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>26.06.12</t>
+          <t>26.06.18</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583975</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584293</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>두원공과대학교</t>
+          <t>이화여자대학교</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AX교양학부 초빙교원 모집</t>
+          <t>경영전문대학원 특임교수 모집</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>26.06.11</t>
+          <t>26.06.13</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584097</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584334</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>경북대학교</t>
+          <t>서울대학교</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026학년도 제2차 교수 초빙</t>
+          <t>천연물과학연구소 연구교원 모집 (8차)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>26.07.21</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>26.07.31</t>
+          <t>26.06.15</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>26.05.27</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3571083</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584290</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>한림대학교</t>
+          <t>전주대학교</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>스타트업비즈니스전공 겸임교원 모집</t>
+          <t>비전임교원 모집</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>내일마감</t>
+          <t>26.06.12</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583981</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584307</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GIST</t>
+          <t>경기과학기술대학교</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>언어교육원 비전임직교원(대우교수) 채용</t>
+          <t>강사 모집</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.01</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>26.06.21</t>
+          <t>26.06.12</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584061</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583926</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>한라대학교</t>
+          <t>부산교육대학교</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>특별교원 모집 (7차)</t>
+          <t>대학원 음악교육과 강사 모집</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.11</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>내일마감</t>
+          <t>26.06.12</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583979</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584276</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>한경국립대학교</t>
+          <t>경북대학교</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>공군학군단 초빙교원 모집</t>
+          <t>장수생활과학연구소 연구초빙교수 모집</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.10</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2701,259 +2693,259 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583980</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584271</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>혜전대학교</t>
+          <t>서울대학교병원</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>교수 초빙</t>
+          <t>의생명연구원 연구교수 모집</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>26.05.29</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>26.06.12</t>
+          <t>26.06.15</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583123</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584264</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DGIST</t>
+          <t>한국폴리텍IV대학</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>초빙강의교수 모집</t>
+          <t>충주캠퍼스 산학협력중점교수 모집</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>26.06.19</t>
+          <t>26.06.21</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583964</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584064</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>세한대학교</t>
+          <t>단국대학교</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>특수신분교원 모집</t>
+          <t>의료원 내과중환자실 임상전담교원 및 촉탁의 모집</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>내일마감</t>
-        </is>
-      </c>
+          <t>채용시까지</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583978</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584100</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>경상국립대학교</t>
+          <t>한영대학교</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>농업생명과학연구원 초빙교원 모집</t>
+          <t>간호학과 강사 모집</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>내일마감</t>
+          <t>26.06.12</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583974</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584144</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>대구과학대학교</t>
+          <t>KAIST</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>간호학과 2026학년도 2학기 전임교원 초빙</t>
+          <t>디지털인문사회과학부 2026학년도 신규 강사 채용</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>26.06.19</t>
+          <t>26.06.15</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584020</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583928</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>신성대학교</t>
+          <t>한국건설인정책연구원</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>전임교원 초빙</t>
+          <t>건설기술인 교육기관 신규강사 인력 풀 모집</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.05.28</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>26.06.19</t>
+          <t>26.06.22</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.01</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583968</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3582935</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>한라대학교</t>
+          <t>서울디지털대학교</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>전임 및 비전임 교원 초빙</t>
+          <t>비전임교원 모집</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>공고문참조</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
+          <t>26.06.10</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>26.06.17</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>26.06.05</t>
@@ -2961,271 +2953,279 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583827</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584033</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>전남대학교</t>
+          <t>인덕대학교</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>인공지능혁신융합대학사업단 비전임교원 모집</t>
+          <t>스마트경영비서학과 강사 모집</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>26.06.02</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>26.06.17</t>
+          <t>26.06.11</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583808</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584146</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>가톨릭대학교</t>
+          <t>국립순천대학교</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>성의교정 가톨릭대학교 인문사회의학과 교원 초빙</t>
+          <t>글로컬대학사업 비전임교원 및 연구원 모집</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>공고문참조</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
+          <t>26.06.05</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>26.06.12</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583805</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584101</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>서울대학교</t>
+          <t>동명대학교</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>공과대학 협동과정 기술경영경제정책 전공 외국인 교원 인재풀 모집</t>
+          <t>교육혁신센터 초빙교수 모집</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>공고문참조</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
+          <t>26.06.05</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>26.06.12</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583951</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583975</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>서울대학교</t>
+          <t>GWP임용학원</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>국제농업기술대학원 특임교원 모집</t>
+          <t>임용시험 전문 강사 공개 채용</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>26.06.04</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>내일마감</t>
-        </is>
-      </c>
+          <t>채용시까지</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583918</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584065</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>이화여자대학교</t>
+          <t>두원공과대학교</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>이화인문과학원 인문사회학술연구교수 모집</t>
+          <t>AX교양학부 초빙교원 모집</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>내일마감</t>
+          <t>26.06.11</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583908</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584097</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>한양대학교</t>
+          <t>충북대학교</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ERICA캠퍼스 겸임교수/강사 모집</t>
+          <t>소프트웨어학부 계절수업 강사 모집</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>관련URL참조</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr"/>
+          <t>26.06.05</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>오늘마감</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583718</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583982</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>연세대학교</t>
+          <t>한림대학교</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>법학전문대학원 비전임교원 모집</t>
+          <t>스타트업비즈니스전공 겸임교원 모집</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>26.06.02</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>26.06.15</t>
+          <t>내일마감</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583801</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583981</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>KAIST</t>
+          <t>한경국립대학교</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>디지털인문사회과학부 2026학년도 신규 강사 채용</t>
+          <t>공군학군단 초빙교원 모집</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3235,219 +3235,215 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>26.06.15</t>
+          <t>26.06.11</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583928</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583980</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>한국교원대학교</t>
+          <t>KAIST</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>초빙교원 모집</t>
+          <t>디지털인문사회과학부 가을학기 강사 모집</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>26.06.18</t>
+          <t>26.06.15</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584240</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583983</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>서울외국어대학원대학교</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>겸임/특임교원 모집</t>
+          <t>기술강사 모집</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>26.06.15</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>26.06.26</t>
-        </is>
-      </c>
+          <t>관련URL참조</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583976</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583392</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>한국폴리텍특성화대학</t>
+          <t>DGIST</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>반도체융합캠퍼스 산학협력중점교수 모집</t>
+          <t>초빙강의교수 모집</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>26.06.18</t>
+          <t>26.06.19</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584273</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583964</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>연세대학교</t>
+          <t>세한대학교</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>간호대학 LT강사 모집</t>
+          <t>특수신분교원 모집</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>26.06.19</t>
+          <t>내일마감</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584283</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583978</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>서울대학교</t>
+          <t>경상국립대학교</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>사범대학 강사 모집 (2차 추가)</t>
+          <t>농업생명과학연구원 초빙교원 모집</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>26.06.11</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>26.06.18</t>
+          <t>내일마감</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584293</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583974</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>이화여자대학교</t>
+          <t>(GB)글로벌이노에듀</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>경영전문대학원 특임교수 모집</t>
+          <t>사회복지현장실습 교·강사 모집</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3457,76 +3453,76 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>26.06.13</t>
+          <t>26.06.21</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584334</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583870</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>서울대학교</t>
+          <t>순천제일대학교</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>천연물과학연구소 연구교원 모집 (8차)</t>
+          <t>한국어센터 한국어강사 모집</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.01</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>26.06.15</t>
+          <t>26.06.12</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584290</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583923</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>전주대학교</t>
+          <t>연세대학교</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>비전임교원 모집</t>
+          <t>원주의과대학 피부과학교실 임상강사 모집</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3536,395 +3532,387 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584307</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583904</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>경기과학기술대학교</t>
+          <t>전남대학교</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>강사 모집</t>
+          <t>인공지능혁신융합대학사업단 비전임교원 모집</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>26.06.01</t>
+          <t>26.06.02</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>26.06.12</t>
+          <t>26.06.17</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583926</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583808</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>부산교육대학교</t>
+          <t>서울대학교</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>대학원 음악교육과 강사 모집</t>
+          <t>국제농업기술대학원 특임교원 모집</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>26.06.11</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>26.06.12</t>
+          <t>내일마감</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584276</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583918</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>경북대학교</t>
+          <t>한양대학교</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>장수생활과학연구소 연구초빙교수 모집</t>
+          <t>ERICA캠퍼스 겸임교수/강사 모집</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>26.06.10</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>26.06.11</t>
-        </is>
-      </c>
+          <t>관련URL참조</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584271</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583718</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>서울대학교병원</t>
+          <t>가톨릭대학교</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>의생명연구원 연구교수 모집</t>
+          <t>성심교정 강사 모집</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>26.06.15</t>
+          <t>내일마감</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584264</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583899</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>한국폴리텍IV대학</t>
+          <t>대경대학교</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>충주캠퍼스 산학협력중점교수 모집</t>
+          <t>글로벌어학센터 한국어강사 모집</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>26.06.21</t>
+          <t>오늘마감</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584064</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583900</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>단국대학교</t>
+          <t>배재대학교</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>의료원 내과중환자실 임상전담교원 및 촉탁의 모집</t>
+          <t>강사 모집</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>채용시까지</t>
+          <t>공고문참조</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584100</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583901</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>한영대학교</t>
+          <t>연세대학교</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>간호학과 강사 모집</t>
+          <t>법학전문대학원 비전임교원 모집</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.02</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>26.06.12</t>
+          <t>26.06.15</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584144</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583801</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>한국건설인정책연구원</t>
+          <t>연세대학교</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>건설기술인 교육기관 신규강사 인력 풀 모집</t>
+          <t>약학대학 학문후속세대강사 모집</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>26.05.28</t>
+          <t>26.06.02</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>26.06.22</t>
+          <t>내일마감</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>26.06.01</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3582935</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583807</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>서울디지털대학교</t>
+          <t>강서대학교</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>비전임교원 모집</t>
+          <t>강사 모집</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>26.06.10</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>26.06.17</t>
+          <t>오늘마감</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584033</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583812</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>인덕대학교</t>
+          <t>한림성심대학교</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>스마트경영비서학과 강사 모집</t>
+          <t>2026학년도 2학기 전임교원, 비전임교원(겸임), 강사 초빙</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>26.06.11</t>
-        </is>
-      </c>
+          <t>관련URL참조</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584146</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583109</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>국립순천대학교</t>
+          <t>서울대학교</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>글로컬대학사업 비전임교원 및 연구원 모집</t>
+          <t>약학대학 강사 모집</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3939,104 +3927,108 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584101</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583697</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>동명대학교</t>
+          <t>아주자동차대학교</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>교육혁신센터 초빙교수 모집</t>
+          <t>글로벌어학센터 영어강사 모집</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.01</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>26.06.12</t>
+          <t>내일마감</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583975</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583724</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>GWP임용학원</t>
+          <t>대교에듀스퀘어(대교해밀평생교육원)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>임용시험 전문 강사 공개 채용</t>
+          <t>학점은행제 운영 교강사 모집</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>채용시까지</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
+          <t>26.06.02</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>26.06.21</t>
+        </is>
+      </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584065</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583608</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>두원공과대학교</t>
+          <t>한국교원대학교</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AX교양학부 초빙교원 모집</t>
+          <t>강사 모집</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.02</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4046,34 +4038,34 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.02</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584097</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583588</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>충북대학교</t>
+          <t>목포가톨릭대학교</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>소프트웨어학부 계절수업 강사 모집</t>
+          <t>강사 모집</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.01</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4083,178 +4075,182 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.02</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583982</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583690</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>한림대학교</t>
+          <t>차의과학대학교</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>스타트업비즈니스전공 겸임교원 모집</t>
+          <t>강사 모집</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.01</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>내일마감</t>
+          <t>26.06.21</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.02</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583981</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583575</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>224</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>한경국립대학교</t>
+          <t>한국전력공사</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>공군학군단 초빙교원 모집</t>
+          <t>2026년도 제2차 전문직원 채용</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.09</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>26.06.11</t>
+          <t>26.06.16</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.09</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583980</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583939</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>223</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>KAIST</t>
+          <t>나노종합기술원</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>디지털인문사회과학부 가을학기 강사 모집</t>
+          <t>반도체 분야 해외(IMEC) 인턴쉽 사업 연수 파견생 모집 공고</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.05.26</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>26.06.15</t>
+          <t>26.06.26</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583983</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584352</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>222</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>밀리사이트테크놀러지스</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>기술강사 모집</t>
+          <t>RF / 초고주파 연구개발 핵심 인력 채용 (연구 실무자급)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>관련URL참조</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
+          <t>26.06.04</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>26.07.03</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583392</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584168</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>221</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DGIST</t>
+          <t>한국생명공학연구원</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>초빙강의교수 모집</t>
+          <t>2026-3차 계약직(연구원/기술원/사무원) 채용</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4264,66 +4260,62 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583964</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584254</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>220</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>세한대학교</t>
+          <t>UNIST</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>특수신분교원 모집</t>
+          <t>하이퍼-컴포저블 데이터센터 연구센터 박사급 연구원 모집</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>내일마감</t>
-        </is>
-      </c>
+          <t>채용시까지</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583978</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3567381</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>219</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>경상국립대학교</t>
+          <t>한국교육환경보호원</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>농업생명과학연구원 초빙교원 모집</t>
+          <t>일반직 및 기간제 근로자 채용 재공고</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4333,693 +4325,701 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>내일마감</t>
+          <t>26.06.15</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583974</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583871</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>218</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>(GB)글로벌이노에듀</t>
+          <t>고려대학교</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>사회복지현장실습 교·강사 모집</t>
+          <t>미래성장연구원 연구교수/박사후연구원 임용</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>26.06.21</t>
+          <t>26.06.15</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583870</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584196</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>217</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>순천제일대학교</t>
+          <t>수원대학교</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>한국어센터 한국어강사 모집</t>
+          <t>전공설계지원센터 계약직 연구원 모집</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>26.06.01</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>26.06.12</t>
+          <t>26.06.17</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583923</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584346</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>216</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>연세대학교</t>
+          <t>신라대학교</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>원주의과대학 피부과학교실 임상강사 모집</t>
+          <t>진로개발센터 계약직 연구원 모집</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>26.06.12</t>
+          <t>26.06.15</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583904</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584287</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>215</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>전남대학교</t>
+          <t>연세대학교</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>인공지능혁신융합대학사업단 비전임교원 모집</t>
+          <t>국어국문학과 학술연구교수 모집</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>26.06.02</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>26.06.17</t>
+          <t>26.06.23</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583808</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584335</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>214</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>서울대학교</t>
+          <t>대한상공회의소</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>국제농업기술대학원 특임교원 모집</t>
+          <t>경영회계사무 인적자원개발위원회 연구원 모집</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>내일마감</t>
+          <t>26.06.14</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583918</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584272</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>한양대학교</t>
+          <t>부산장신대학교</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ERICA캠퍼스 겸임교수/강사 모집</t>
+          <t>CLIPS교육혁신센터 전담연구원 모집</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>관련URL참조</t>
+          <t>채용시까지</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583718</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584281</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>212</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>가톨릭대학교</t>
+          <t>한국건강증진개발원</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>성심교정 강사 모집</t>
+          <t>위촉전문원 모집</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>내일마감</t>
+          <t>26.06.19</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583899</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584087</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>211</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>대경대학교</t>
+          <t>국립목포대학교</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>글로벌어학센터 한국어강사 모집</t>
+          <t>계약직 연구원 모집</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>오늘마감</t>
+          <t>26.06.15</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583900</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584296</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>배재대학교</t>
+          <t>국립순천대학교</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>강사 모집</t>
+          <t>글로벌지역혁신전략연구센터 연구원 모집</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>공고문참조</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>26.06.02</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>26.06.15</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583901</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584255</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>209</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>연세대학교</t>
+          <t>강원대학교</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>법학전문대학원 비전임교원 모집</t>
+          <t>대학혁신지원과 계약직 연구원 모집</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>26.06.02</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>26.06.15</t>
+          <t>26.06.12</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583801</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584311</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>208</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>연세대학교</t>
+          <t>국가첨단백신개발센터</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>약학대학 학문후속세대강사 모집</t>
+          <t>직원 모집</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>26.06.02</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>내일마감</t>
+          <t>26.06.19</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583807</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584145</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>207</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>강서대학교</t>
+          <t>국립한밭대학교</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>강사 모집</t>
+          <t>국립대학육성사업 연구원 모집</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>오늘마감</t>
+          <t>26.06.15</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583812</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584232</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>206</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>한림성심대학교</t>
+          <t>대구대학교</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026학년도 2학기 전임교원, 비전임교원(겸임), 강사 초빙</t>
+          <t>경산교육발전특구사업단 선임연구원 모집</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>관련URL참조</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>26.06.05</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>26.06.14</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583109</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584269</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>205</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>서울대학교</t>
+          <t>경북행복재단</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>약학대학 강사 모집</t>
+          <t>계약직 연구원 모집</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.09</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>26.06.12</t>
+          <t>26.06.15</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583697</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584253</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>204</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>아주자동차대학교</t>
+          <t>연암공과대학교</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>글로벌어학센터 영어강사 모집</t>
+          <t>산학협력단 AID사업단 연구원 모집</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>26.06.01</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>내일마감</t>
+          <t>26.06.15</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583724</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584202</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>203</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>대교에듀스퀘어(대교해밀평생교육원)</t>
+          <t>제이디바이오사이언스</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>학점은행제 운영 교강사 모집</t>
+          <t>연구원 모집</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>26.06.02</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>26.06.21</t>
+          <t>26.06.30</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583608</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584197</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>202</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>한국교원대학교</t>
+          <t>마린유겐트코리아</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>강사 모집</t>
+          <t>연구원 모집</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>26.06.02</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>26.06.11</t>
+          <t>26.07.03</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>26.06.02</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583588</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584025</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>201</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>목포가톨릭대학교</t>
+          <t>고려대학교</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>강사 모집</t>
+          <t>환경생태공학부 옥용식교수연구실 연구원 모집</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>26.06.01</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>오늘마감</t>
+          <t>26.06.26</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>26.06.02</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583690</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584179</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>200</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>차의과학대학교</t>
+          <t>현대종합금속</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>강사 모집</t>
+          <t>중앙연구소 직원 모집</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>26.06.01</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -5029,39 +5029,39 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>26.06.02</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583575</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584163</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>199</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>나노종합기술원</t>
+          <t>한국노인종합복지관협회</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>반도체 분야 해외(IMEC) 인턴쉽 사업 연수 파견생 모집 공고</t>
+          <t>계약직 연구원 모집</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>26.05.26</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>26.06.26</t>
+          <t>26.06.17</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584352</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584175</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>198</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>밀리사이트테크놀러지스</t>
+          <t>이화여자대학교</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>RF / 초고주파 연구개발 핵심 인력 채용 (연구 실무자급)</t>
+          <t>인권센터 연구원 모집</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>26.07.03</t>
+          <t>26.06.16</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5108,24 +5108,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584168</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584161</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>197</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>한국생명공학연구원</t>
+          <t>대한의학회</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-3차 계약직(연구원/기술원/사무원) 채용</t>
+          <t>선임연구원 모집</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>26.06.19</t>
+          <t>26.07.03</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5145,24 +5145,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584254</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584125</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>196</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>UNIST</t>
+          <t>사이키바이오텍</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>하이퍼-컴포저블 데이터센터 연구센터 박사급 연구원 모집</t>
+          <t>기업부설연구소 연구원 모집</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -5178,24 +5178,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3567381</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584229</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>195</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>한국교육환경보호원</t>
+          <t>대구대학교</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>일반직 및 기간제 근로자 채용 재공고</t>
+          <t>RISE사업단 계약직 연구원 모집</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>26.06.15</t>
+          <t>26.06.17</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5215,34 +5215,34 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583871</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584067</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>194</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>고려대학교</t>
+          <t>한국문화관광연구원</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>미래성장연구원 연구교수/박사후연구원 임용</t>
+          <t>Post-Doc./위촉연구원 모집</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>26.06.04</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>26.06.15</t>
+          <t>26.06.19</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5252,34 +5252,34 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584196</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584166</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>193</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>수원대학교</t>
+          <t>강원특별자치도공공보건의료지원단</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>전공설계지원센터 계약직 연구원 모집</t>
+          <t>연구원 모집</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>26.06.17</t>
+          <t>26.06.18</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5289,34 +5289,34 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584346</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584071</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>192</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>신라대학교</t>
+          <t>에코프로에이치엔</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>진로개발센터 계약직 연구원 모집</t>
+          <t>유기소재개발 경력직원 모집</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>26.06.15</t>
+          <t>26.06.17</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5326,34 +5326,34 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584287</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584040</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>191</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>연세대학교</t>
+          <t>국토연구원</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>국어국문학과 학술연구교수 모집</t>
+          <t>위촉직 연구원 모집</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>26.06.23</t>
+          <t>26.06.19</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5363,34 +5363,34 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584335</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584034</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>190</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>대한상공회의소</t>
+          <t>마린유겐트코리아</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>경영회계사무 인적자원개발위원회 연구원 모집</t>
+          <t>연구원 채용</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>26.06.14</t>
+          <t>26.07.03</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5400,32 +5400,36 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584272</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584023</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>189</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>부산장신대학교</t>
+          <t>전남테크노파크</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CLIPS교육혁신센터 전담연구원 모집</t>
+          <t>금속소재융복합센터 위촉연구원 모집</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>채용시까지</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr"/>
+          <t>26.06.01</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>26.06.15</t>
+        </is>
+      </c>
       <c r="F137" t="inlineStr">
         <is>
           <t>26.06.08</t>
@@ -5433,24 +5437,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584281</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584118</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>188</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>한국건강증진개발원</t>
+          <t>제주연구원</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>위촉전문원 모집</t>
+          <t>제주학연구센터 전문연구원 모집</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -5460,7 +5464,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>26.06.19</t>
+          <t>26.06.16</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5470,29 +5474,29 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584087</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584119</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>187</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>국립목포대학교</t>
+          <t>비씨월드제약</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>계약직 연구원 모집</t>
+          <t>직원 모집</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.06</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5507,29 +5511,29 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584296</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584058</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>186</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>국립순천대학교</t>
+          <t>용인시정연구원</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>글로벌지역혁신전략연구센터 연구원 모집</t>
+          <t>2026년 제4회 연구직 공개채용 (재난안전분야, 데이터 사이언스 분야)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>26.06.02</t>
+          <t>26.06.08</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5544,24 +5548,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584255</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583934</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>185</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>강원대학교</t>
+          <t>광주광역시사회서비스원</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>대학혁신지원과 계약직 연구원 모집</t>
+          <t>계약직 연구원/연구보조원 모집</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -5571,34 +5575,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>26.06.12</t>
+          <t>26.06.15</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584311</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584184</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>184</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>국가첨단백신개발센터</t>
+          <t>국립한밭대학교</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>직원 모집</t>
+          <t>AI융합교육원 연구원 및 행정원 모집</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5608,39 +5612,39 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>26.06.19</t>
+          <t>26.06.11</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584145</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584018</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>183</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>국립한밭대학교</t>
+          <t>차병원·바이오그룹</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>국립대학육성사업 연구원 모집</t>
+          <t>임원/경력공채</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.02</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5655,66 +5659,66 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584232</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583791</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>182</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>대구대학교</t>
+          <t>국립산림과학원</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>경산교육발전특구사업단 선임연구원 모집</t>
+          <t>계약직 연구원 모집</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>26.06.14</t>
+          <t>26.06.15</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584269</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584059</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>181</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>경북행복재단</t>
+          <t>중앙대학교</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>계약직 연구원 모집</t>
+          <t>다빈치캠퍼스 RISE사업단 전임연구원 모집</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>26.06.09</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5724,78 +5728,74 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584253</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584038</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>180</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>연암공과대학교</t>
+          <t>아주대학교의료원</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>산학협력단 AID사업단 연구원 모집</t>
+          <t>정신건강의학교실/바이오디지털융합연구소 연구원 모집</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.04</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>26.06.15</t>
+          <t>26.06.12</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584202</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583967</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>179</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>제이디바이오사이언스</t>
+          <t>가천대</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>연구원 모집</t>
+          <t>길병원 예방의학교실 연구원 모집</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>26.06.30</t>
-        </is>
-      </c>
+          <t>채용시까지</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>26.06.08</t>
@@ -5803,135 +5803,135 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584197</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3583965</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>178</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>마린유겐트코리아</t>
+          <t>부산연구원</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>연구원 모집</t>
+          <t>비상임연구원 모집</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.09</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>26.07.03</t>
+          <t>26.06.15</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584025</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584120</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>177</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>고려대학교</t>
+          <t>한림대학교</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>환경생태공학부 옥용식교수연구실 연구원 모집</t>
+          <t>글로벌사회공헌연구소 계약직 연구원 모집</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.03</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>26.06.26</t>
+          <t>26.06.14</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584179</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584111</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>176</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>현대종합금속</t>
+          <t>포항산업과학연구원</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>중앙연구소 직원 모집</t>
+          <t>위촉연구원 모집</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>26.06.05</t>
+          <t>26.06.02</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>26.06.21</t>
+          <t>26.06.14</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584163</t>
+          <t>https://www.hibrain.net/recruitment/recruits/3584170</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>175</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>한국노인종합복지관협회</t>
+          <t>영남대학교</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>계약직 연구원 모집</t>
+          <t>교육혁신센터 계약직 연구원 모집</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -5941,934 +5941,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>26.06.17</t>
+          <t>26.06.11</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>26.06.08</t>
+          <t>26.06.05</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584175</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>이화여자대학교</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>인권센터 연구원 모집</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>26.06.16</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>26.06.08</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584161</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>대한의학회</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>선임연구원 모집</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>26.07.03</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>26.06.08</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584125</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>사이키바이오텍</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>기업부설연구소 연구원 모집</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>채용시까지</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>26.06.08</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584229</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>대구대학교</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>RISE사업단 계약직 연구원 모집</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>26.06.04</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>26.06.17</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>26.06.08</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584067</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>한국문화관광연구원</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Post-Doc./위촉연구원 모집</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>26.06.19</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>26.06.08</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584166</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>강원특별자치도공공보건의료지원단</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>연구원 모집</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>26.06.18</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>26.06.08</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584071</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>에코프로에이치엔</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>유기소재개발 경력직원 모집</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>26.06.04</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>26.06.17</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>26.06.08</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584040</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>국토연구원</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>위촉직 연구원 모집</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>26.06.19</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>26.06.08</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584034</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>마린유겐트코리아</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>연구원 채용</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>26.07.03</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>26.06.08</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584023</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>전남테크노파크</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>금속소재융복합센터 위촉연구원 모집</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>26.06.01</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>26.06.15</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>26.06.08</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584118</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>제주연구원</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>제주학연구센터 전문연구원 모집</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>26.06.16</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>26.06.08</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584119</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>비씨월드제약</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>직원 모집</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>26.06.06</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>26.06.15</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>26.06.08</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584058</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>용인시정연구원</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>2026년 제4회 연구직 공개채용 (재난안전분야, 데이터 사이언스 분야)</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>26.06.08</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>26.06.15</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>26.06.08</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583934</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>광주광역시사회서비스원</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>계약직 연구원/연구보조원 모집</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>26.06.08</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>26.06.15</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584184</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>국립한밭대학교</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>AI융합교육원 연구원 및 행정원 모집</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>26.06.11</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584018</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>차병원·바이오그룹</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>임원/경력공채</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>26.06.02</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>26.06.15</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>26.06.08</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583791</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>국립산림과학원</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>계약직 연구원 모집</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>26.06.04</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>26.06.15</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584059</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>중앙대학교</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>다빈치캠퍼스 RISE사업단 전임연구원 모집</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>26.06.15</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584038</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>아주대학교의료원</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>정신건강의학교실/바이오디지털융합연구소 연구원 모집</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>26.06.04</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>26.06.12</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583967</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>가천대</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>길병원 예방의학교실 연구원 모집</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>채용시까지</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>26.06.08</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3583965</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>부산연구원</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>비상임연구원 모집</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>26.06.09</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>26.06.15</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584120</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>한림대학교</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>글로벌사회공헌연구소 계약직 연구원 모집</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>26.06.03</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>26.06.14</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584111</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>포항산업과학연구원</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>위촉연구원 모집</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>26.06.02</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>26.06.14</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584170</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>영남대학교</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>교육혁신센터 계약직 연구원 모집</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>26.06.11</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
           <t>https://www.hibrain.net/recruitment/recruits/3584128</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>한경국립대학교</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>국립대학육성사업 계약직 직원/연구원 모집</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>26.06.04</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>26.06.11</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>26.06.05</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>https://www.hibrain.net/recruitment/recruits/3584026</t>
         </is>
       </c>
     </row>
